--- a/output/Hainan/三亚市_news.xlsx
+++ b/output/Hainan/三亚市_news.xlsx
@@ -547,9 +547,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>False</t>
@@ -561,10 +559,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -613,9 +611,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>False</t>
@@ -627,10 +623,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
         <v>8</v>
@@ -679,9 +675,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>False</t>
@@ -693,7 +687,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" t="n">
         <v>23</v>
@@ -745,9 +739,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>False</t>
@@ -811,9 +803,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>False</t>
@@ -877,9 +867,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>False</t>
@@ -943,9 +931,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1009,9 +995,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1075,9 +1059,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1141,9 +1123,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1151,14 +1131,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>['xlsx,doc,docx']</t>
+          <t>['doc,docx,xlsx']</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1207,9 +1187,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1273,9 +1251,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1283,14 +1259,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>['xlsx,doc,docx']</t>
+          <t>['doc,docx,xlsx']</t>
         </is>
       </c>
       <c r="L13" t="n">
         <v>20</v>
       </c>
       <c r="M13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1339,9 +1315,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1405,9 +1379,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1471,9 +1443,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1485,10 +1455,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1537,9 +1507,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>False</t>
@@ -1603,9 +1571,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>False</t>
@@ -1640,13 +1606,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">市直属学校基本名录 </t>
+          <t>市直属学校基本名录</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">市直属学校基本名录 </t>
+          <t>市直属学校基本名录</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1669,9 +1635,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>False</t>
@@ -1693,7 +1657,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dataopen1.sanya.gov.cn/#/elmDataList?id=c92lr2vil8ta60m98gp0=市直属学校基本名录 </t>
+          <t>https://dataopen1.sanya.gov.cn/#/elmDataList?id=c92lr2vil8ta60m98gp0=市直属学校基本名录</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -1735,9 +1699,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>False</t>
@@ -1801,9 +1763,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>False</t>
@@ -1867,9 +1827,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>False</t>
@@ -1884,7 +1842,7 @@
         <v>20</v>
       </c>
       <c r="M22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1933,9 +1891,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>False</t>
@@ -1999,9 +1955,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2065,9 +2019,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2131,9 +2083,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2197,9 +2147,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2263,9 +2211,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>False</t>
@@ -2329,9 +2275,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>False</t>
@@ -2395,9 +2339,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>False</t>
@@ -2461,9 +2403,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>False</t>
@@ -2527,9 +2467,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>False</t>
@@ -2593,9 +2531,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>False</t>
@@ -2659,9 +2595,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>False</t>
@@ -2725,9 +2659,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>False</t>
@@ -2791,9 +2723,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>False</t>
@@ -2857,9 +2787,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>False</t>
@@ -2874,7 +2802,7 @@
         <v>20</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
@@ -2923,9 +2851,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>False</t>
@@ -2989,9 +2915,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>False</t>
@@ -3055,9 +2979,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>False</t>
@@ -3121,9 +3043,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>False</t>
@@ -3187,9 +3107,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>False</t>
@@ -3204,7 +3122,7 @@
         <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3253,9 +3171,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>False</t>
@@ -3319,9 +3235,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>False</t>
@@ -3385,9 +3299,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>False</t>
@@ -3451,9 +3363,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>False</t>
@@ -3517,9 +3427,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>False</t>
@@ -3583,9 +3491,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>False</t>
@@ -3649,9 +3555,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>False</t>
@@ -3715,9 +3619,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>False</t>
@@ -3781,9 +3683,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>False</t>
@@ -3847,9 +3747,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>False</t>
@@ -3913,9 +3811,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>False</t>
@@ -3979,9 +3875,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>False</t>
@@ -4045,9 +3939,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>False</t>
@@ -4111,9 +4003,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>False</t>
@@ -4177,9 +4067,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>False</t>
@@ -4243,9 +4131,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>False</t>
@@ -4309,9 +4195,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>False</t>
@@ -4375,9 +4259,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>False</t>
@@ -4441,9 +4323,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>False</t>
@@ -4507,9 +4387,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>False</t>
@@ -4573,9 +4451,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>False</t>
@@ -4639,9 +4515,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>False</t>
@@ -4705,9 +4579,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>False</t>
@@ -4771,9 +4643,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>False</t>
@@ -4837,9 +4707,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>False</t>
@@ -4903,9 +4771,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>False</t>
@@ -4920,7 +4786,7 @@
         <v>24</v>
       </c>
       <c r="M68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N68" t="n">
         <v>5</v>
@@ -4969,9 +4835,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>False</t>
@@ -5035,9 +4899,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>False</t>
@@ -5101,9 +4963,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>False</t>
@@ -5167,9 +5027,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>False</t>
@@ -5233,9 +5091,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>False</t>
@@ -5299,9 +5155,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>False</t>
@@ -5365,9 +5219,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>False</t>
@@ -5431,9 +5283,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>False</t>
@@ -5497,9 +5347,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>False</t>
@@ -5507,7 +5355,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>['docx,xlsx']</t>
+          <t>['xlsx,docx']</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -5563,9 +5411,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>False</t>
@@ -5577,7 +5423,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M78" t="n">
         <v>1</v>
@@ -5629,9 +5475,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>False</t>
@@ -5695,9 +5539,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>False</t>
@@ -5761,9 +5603,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>False</t>
@@ -5827,9 +5667,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>False</t>
@@ -5893,9 +5731,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>False</t>
@@ -5959,9 +5795,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>False</t>
@@ -5976,7 +5810,7 @@
         <v>5</v>
       </c>
       <c r="M84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -6025,9 +5859,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>False</t>
@@ -6039,10 +5871,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N85" t="n">
         <v>1</v>
@@ -6091,9 +5923,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>False</t>
@@ -6105,10 +5935,10 @@
         </is>
       </c>
       <c r="L86" t="n">
+        <v>6</v>
+      </c>
+      <c r="M86" t="n">
         <v>5</v>
-      </c>
-      <c r="M86" t="n">
-        <v>4</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -6157,9 +5987,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>False</t>
@@ -6223,9 +6051,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>False</t>
@@ -6289,9 +6115,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>False</t>
@@ -6355,9 +6179,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>False</t>
@@ -6421,9 +6243,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>False</t>
@@ -6487,9 +6307,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>False</t>
@@ -6553,9 +6371,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>False</t>
@@ -6619,9 +6435,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>False</t>
@@ -6685,9 +6499,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>False</t>
@@ -6751,9 +6563,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>False</t>
@@ -6817,9 +6627,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>False</t>
@@ -6883,9 +6691,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>False</t>
@@ -6949,9 +6755,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>False</t>
@@ -7015,9 +6819,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>False</t>
@@ -7081,9 +6883,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>False</t>
@@ -7147,9 +6947,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>False</t>
@@ -7213,9 +7011,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>False</t>
@@ -7279,9 +7075,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>False</t>
@@ -7345,9 +7139,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>False</t>
@@ -7411,9 +7203,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>False</t>
@@ -7477,9 +7267,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>False</t>
@@ -7487,7 +7275,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>['doc,pdf']</t>
+          <t>['pdf,doc']</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -7543,9 +7331,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>False</t>
@@ -7609,9 +7395,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>False</t>
@@ -7675,9 +7459,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>False</t>
@@ -7741,9 +7523,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>False</t>
@@ -7807,9 +7587,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>False</t>
@@ -7824,7 +7602,7 @@
         <v>666</v>
       </c>
       <c r="M112" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N112" t="n">
         <v>12</v>
@@ -7873,9 +7651,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>False</t>
@@ -7939,9 +7715,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>False</t>
@@ -7953,7 +7727,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M114" t="n">
         <v>841</v>
@@ -8005,9 +7779,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>False</t>
@@ -8071,9 +7843,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>False</t>
@@ -8137,9 +7907,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>False</t>
@@ -8203,9 +7971,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>False</t>
@@ -8269,9 +8035,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>False</t>
@@ -8335,9 +8099,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>False</t>
@@ -8401,9 +8163,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>False</t>
@@ -8467,9 +8227,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>False</t>
@@ -8533,9 +8291,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>False</t>
@@ -8599,9 +8355,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>False</t>
@@ -8665,9 +8419,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>False</t>
@@ -8731,9 +8483,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>False</t>
@@ -8748,7 +8498,7 @@
         <v>284</v>
       </c>
       <c r="M126" t="n">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="N126" t="n">
         <v>3</v>
@@ -8797,9 +8547,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>False</t>
@@ -8863,9 +8611,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>False</t>
@@ -8929,9 +8675,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>False</t>
@@ -8995,9 +8739,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>False</t>
@@ -9061,9 +8803,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>False</t>
@@ -9127,9 +8867,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>False</t>
@@ -9193,9 +8931,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>False</t>
@@ -9259,9 +8995,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>False</t>
@@ -9325,9 +9059,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>False</t>
@@ -9391,9 +9123,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>False</t>
@@ -9457,9 +9187,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>False</t>
@@ -9474,7 +9202,7 @@
         <v>105</v>
       </c>
       <c r="M137" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N137" t="n">
         <v>4</v>
@@ -9523,9 +9251,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>False</t>
@@ -9589,9 +9315,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>False</t>
@@ -9655,9 +9379,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>False</t>
@@ -9721,9 +9443,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>False</t>
@@ -9787,9 +9507,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>False</t>
@@ -9853,9 +9571,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>False</t>
@@ -9919,9 +9635,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>False</t>
@@ -9985,9 +9699,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>0</v>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>False</t>
@@ -10051,9 +9763,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>False</t>
@@ -10065,10 +9775,10 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M146" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N146" t="n">
         <v>0</v>
@@ -10117,9 +9827,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>False</t>
@@ -10183,9 +9891,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>False</t>
@@ -10200,7 +9906,7 @@
         <v>108</v>
       </c>
       <c r="M148" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N148" t="n">
         <v>2</v>
@@ -10249,9 +9955,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>False</t>
@@ -10315,9 +10019,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>False</t>
@@ -10381,9 +10083,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>False</t>
@@ -10447,9 +10147,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>False</t>
@@ -10464,7 +10162,7 @@
         <v>108</v>
       </c>
       <c r="M152" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N152" t="n">
         <v>3</v>
@@ -10513,9 +10211,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>False</t>
@@ -10579,9 +10275,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>False</t>
@@ -10589,7 +10283,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>['xlsx,doc']</t>
+          <t>['doc,xlsx']</t>
         </is>
       </c>
       <c r="L154" t="n">
@@ -10645,9 +10339,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>False</t>
@@ -10659,10 +10351,10 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M155" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
@@ -10711,9 +10403,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>False</t>
@@ -10777,9 +10467,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>False</t>
@@ -10843,9 +10531,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>False</t>
@@ -10860,7 +10546,7 @@
         <v>147</v>
       </c>
       <c r="M158" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N158" t="n">
         <v>17</v>
@@ -10909,9 +10595,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I159" t="n">
-        <v>0</v>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>False</t>
@@ -10975,9 +10659,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>False</t>
@@ -11041,9 +10723,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>False</t>
@@ -11107,9 +10787,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>False</t>
@@ -11173,9 +10851,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>False</t>
@@ -11239,9 +10915,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>False</t>
@@ -11305,9 +10979,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>False</t>
@@ -11371,9 +11043,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>False</t>
@@ -11437,9 +11107,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>False</t>
@@ -11503,9 +11171,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>False</t>
@@ -11569,9 +11235,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>0</v>
-      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>False</t>
@@ -11635,9 +11299,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I170" t="n">
-        <v>0</v>
-      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>False</t>
@@ -11701,9 +11363,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>False</t>
@@ -11767,9 +11427,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>False</t>
@@ -11833,9 +11491,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>False</t>
@@ -11899,9 +11555,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>0</v>
-      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>False</t>
@@ -11965,9 +11619,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I175" t="n">
-        <v>0</v>
-      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>False</t>
@@ -12031,9 +11683,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I176" t="n">
-        <v>0</v>
-      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>False</t>
@@ -12097,9 +11747,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I177" t="n">
-        <v>0</v>
-      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>False</t>
@@ -12163,9 +11811,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I178" t="n">
-        <v>0</v>
-      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>False</t>
@@ -12229,9 +11875,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>False</t>
@@ -12295,9 +11939,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>0</v>
-      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>False</t>
@@ -12361,9 +12003,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>0</v>
-      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>False</t>
@@ -12427,9 +12067,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>0</v>
-      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>False</t>
@@ -12493,9 +12131,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I183" t="n">
-        <v>0</v>
-      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>False</t>
@@ -12559,9 +12195,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>0</v>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>False</t>
@@ -12625,9 +12259,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>0</v>
-      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>False</t>
@@ -12691,9 +12323,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I186" t="n">
-        <v>0</v>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>False</t>
@@ -12757,9 +12387,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>False</t>
@@ -12823,9 +12451,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I188" t="n">
-        <v>0</v>
-      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>False</t>
@@ -12889,9 +12515,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I189" t="n">
-        <v>0</v>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>False</t>
@@ -12955,9 +12579,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I190" t="n">
-        <v>0</v>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>False</t>
@@ -13021,9 +12643,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>0</v>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>False</t>
@@ -13087,9 +12707,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I192" t="n">
-        <v>0</v>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>False</t>
@@ -13153,9 +12771,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>False</t>
@@ -13219,9 +12835,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I194" t="n">
-        <v>0</v>
-      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>False</t>
@@ -13285,9 +12899,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>0</v>
-      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>False</t>
@@ -13351,9 +12963,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>False</t>
@@ -13417,9 +13027,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>False</t>
@@ -13483,9 +13091,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I198" t="n">
-        <v>0</v>
-      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>False</t>
@@ -13549,9 +13155,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I199" t="n">
-        <v>0</v>
-      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>False</t>
@@ -13615,9 +13219,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I200" t="n">
-        <v>0</v>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>False</t>
@@ -13681,9 +13283,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I201" t="n">
-        <v>0</v>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>False</t>
@@ -13747,9 +13347,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I202" t="n">
-        <v>0</v>
-      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>False</t>
@@ -13813,9 +13411,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I203" t="n">
-        <v>0</v>
-      </c>
+      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>False</t>
@@ -13850,7 +13446,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">三亚市正常运行大中型沼气工程 统计表 </t>
+          <t>三亚市正常运行大中型沼气工程 统计表</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -13879,9 +13475,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I204" t="n">
-        <v>0</v>
-      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>False</t>
@@ -13903,7 +13497,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dataopen1.sanya.gov.cn/#/elmDataList?id=c81oqmfil8t8671a04r0=三亚市正常运行大中型沼气工程 统计表 </t>
+          <t>https://dataopen1.sanya.gov.cn/#/elmDataList?id=c81oqmfil8t8671a04r0=三亚市正常运行大中型沼气工程 统计表</t>
         </is>
       </c>
       <c r="P204" t="inlineStr"/>
@@ -13945,9 +13539,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I205" t="n">
-        <v>0</v>
-      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>False</t>
@@ -14011,9 +13603,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I206" t="n">
-        <v>0</v>
-      </c>
+      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>False</t>
@@ -14077,9 +13667,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>False</t>
@@ -14143,9 +13731,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I208" t="n">
-        <v>0</v>
-      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>False</t>
@@ -14209,9 +13795,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I209" t="n">
-        <v>0</v>
-      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>False</t>
@@ -14275,9 +13859,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I210" t="n">
-        <v>0</v>
-      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>False</t>
@@ -14341,9 +13923,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I211" t="n">
-        <v>0</v>
-      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>False</t>
@@ -14407,9 +13987,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I212" t="n">
-        <v>0</v>
-      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>False</t>
@@ -14473,9 +14051,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I213" t="n">
-        <v>0</v>
-      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>False</t>
@@ -14539,9 +14115,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I214" t="n">
-        <v>0</v>
-      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>False</t>
@@ -14605,9 +14179,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I215" t="n">
-        <v>0</v>
-      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>False</t>
@@ -14619,10 +14191,10 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M215" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N215" t="n">
         <v>5</v>
@@ -14671,9 +14243,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I216" t="n">
-        <v>0</v>
-      </c>
+      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>False</t>
@@ -14737,9 +14307,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I217" t="n">
-        <v>0</v>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>False</t>
@@ -14803,9 +14371,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I218" t="n">
-        <v>0</v>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>False</t>
@@ -14869,9 +14435,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I219" t="n">
-        <v>0</v>
-      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>False</t>
@@ -14935,9 +14499,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I220" t="n">
-        <v>0</v>
-      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>False</t>
@@ -15001,9 +14563,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I221" t="n">
-        <v>0</v>
-      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>False</t>
@@ -15067,9 +14627,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I222" t="n">
-        <v>0</v>
-      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>False</t>
@@ -15133,9 +14691,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I223" t="n">
-        <v>0</v>
-      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>False</t>
@@ -15199,9 +14755,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I224" t="n">
-        <v>0</v>
-      </c>
+      <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>False</t>
@@ -15265,9 +14819,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I225" t="n">
-        <v>0</v>
-      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>False</t>
@@ -15331,9 +14883,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I226" t="n">
-        <v>0</v>
-      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>False</t>
@@ -15397,9 +14947,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I227" t="n">
-        <v>0</v>
-      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>False</t>
@@ -15463,9 +15011,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I228" t="n">
-        <v>0</v>
-      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>False</t>
@@ -15529,9 +15075,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I229" t="n">
-        <v>0</v>
-      </c>
+      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>False</t>
@@ -15595,9 +15139,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I230" t="n">
-        <v>0</v>
-      </c>
+      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>False</t>
@@ -15661,9 +15203,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I231" t="n">
-        <v>0</v>
-      </c>
+      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>False</t>
@@ -15727,9 +15267,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I232" t="n">
-        <v>0</v>
-      </c>
+      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>False</t>
@@ -15793,9 +15331,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I233" t="n">
-        <v>0</v>
-      </c>
+      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>False</t>
@@ -15859,9 +15395,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I234" t="n">
-        <v>0</v>
-      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>False</t>
@@ -15876,7 +15410,7 @@
         <v>81</v>
       </c>
       <c r="M234" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N234" t="n">
         <v>4</v>
@@ -15925,9 +15459,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I235" t="n">
-        <v>0</v>
-      </c>
+      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>False</t>
@@ -15991,9 +15523,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I236" t="n">
-        <v>0</v>
-      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>False</t>
@@ -16008,7 +15538,7 @@
         <v>149</v>
       </c>
       <c r="M236" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N236" t="n">
         <v>4</v>
@@ -16057,9 +15587,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I237" t="n">
-        <v>0</v>
-      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>False</t>
@@ -16123,9 +15651,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I238" t="n">
-        <v>0</v>
-      </c>
+      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>False</t>
@@ -16189,9 +15715,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I239" t="n">
-        <v>0</v>
-      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>False</t>
@@ -16255,9 +15779,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I240" t="n">
-        <v>0</v>
-      </c>
+      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>False</t>
@@ -16321,9 +15843,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I241" t="n">
-        <v>0</v>
-      </c>
+      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>False</t>
@@ -16387,9 +15907,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I242" t="n">
-        <v>0</v>
-      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>False</t>
@@ -16453,9 +15971,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I243" t="n">
-        <v>0</v>
-      </c>
+      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>False</t>
@@ -16519,9 +16035,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I244" t="n">
-        <v>0</v>
-      </c>
+      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>False</t>
@@ -16585,9 +16099,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I245" t="n">
-        <v>0</v>
-      </c>
+      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>False</t>
@@ -16651,9 +16163,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I246" t="n">
-        <v>0</v>
-      </c>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>False</t>
@@ -16717,9 +16227,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I247" t="n">
-        <v>0</v>
-      </c>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>False</t>
@@ -16727,7 +16235,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>['xls,xlsx']</t>
+          <t>['xlsx,xls']</t>
         </is>
       </c>
       <c r="L247" t="n">
@@ -16783,9 +16291,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I248" t="n">
-        <v>0</v>
-      </c>
+      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>False</t>
@@ -16849,9 +16355,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I249" t="n">
-        <v>0</v>
-      </c>
+      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>False</t>
@@ -16915,9 +16419,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I250" t="n">
-        <v>0</v>
-      </c>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>False</t>
@@ -16981,9 +16483,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I251" t="n">
-        <v>0</v>
-      </c>
+      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>False</t>
@@ -17047,9 +16547,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I252" t="n">
-        <v>0</v>
-      </c>
+      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>False</t>
@@ -17113,9 +16611,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I253" t="n">
-        <v>0</v>
-      </c>
+      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>False</t>
@@ -17179,9 +16675,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I254" t="n">
-        <v>0</v>
-      </c>
+      <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>False</t>
@@ -17245,9 +16739,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I255" t="n">
-        <v>0</v>
-      </c>
+      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>False</t>
@@ -17311,9 +16803,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I256" t="n">
-        <v>0</v>
-      </c>
+      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>False</t>
@@ -17325,10 +16815,10 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M256" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N256" t="n">
         <v>11</v>
@@ -17377,9 +16867,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I257" t="n">
-        <v>0</v>
-      </c>
+      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>False</t>
@@ -17443,9 +16931,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I258" t="n">
-        <v>0</v>
-      </c>
+      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>False</t>
